--- a/港岛-半山区东部-Central Peak I/Central Peak I_销控明细表.xlsx
+++ b/港岛-半山区东部-Central Peak I/Central Peak I_销控明细表.xlsx
@@ -925,7 +925,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2020-12-06</t>
+          <t>2020-12-07</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -991,7 +991,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2020-12-07</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2021-01-04</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4602,7 +4602,7 @@
           <t>MANOR A | 2005呎 (4+房)
 $17260万
 $86,085/呎
-(20年-12月-07日)</t>
+(20年-12月-08日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4610,7 +4610,7 @@
           <t>MANOR B | 2080呎 (4+房)
 $16380万
 $78,750/呎
-(20年-12月-06日)</t>
+(20年-12月-07日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -4660,7 +4660,7 @@
           <t>MANOR B | 1985呎 (3房)
 $15600万
 $78,589/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -4860,7 +4860,7 @@
           <t>MANOR A | 1985呎 (4+房)
 $18800万
 $94,710/呎
-(21年-01月-04日)</t>
+(21年-01月-05日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4868,7 +4868,7 @@
           <t>MANOR B | 1985呎 (4+房)
 $17600万
 $88,665/呎
-(21年-01月-04日)</t>
+(21年-01月-05日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5099,7 +5099,7 @@
           <t>SKY MANOR | 2627呎 (4+房)
 $28800万
 $109,631/呎
-(22年-06月-14日)</t>
+(22年-06月-15日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
           <t>MANOR B | 2080呎 (4+房)
 $17700万
 $85,096/呎
-(23年-04月-10日)</t>
+(23年-04月-11日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5659,7 +5659,7 @@
           <t>MANOR B | 1615呎 (3房)
 $12920万
 $80,000/呎
-(21年-01月-04日)</t>
+(21年-01月-05日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
